--- a/assets/app_hyup/excel/G_estimate_excel.xlsx
+++ b/assets/app_hyup/excel/G_estimate_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\jmtech\assets\app_hyup\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1972F788-6B48-48F4-AD23-2E9ED535603A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320C8F83-D68A-4366-B2B8-1FAB10F0CA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="21600" windowHeight="11295" xr2:uid="{A8E3B584-EFA5-47FD-B92C-1698FC3C9E4C}"/>
+    <workbookView xWindow="7605" yWindow="930" windowWidth="21600" windowHeight="11295" xr2:uid="{A8E3B584-EFA5-47FD-B92C-1698FC3C9E4C}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
@@ -917,6 +917,147 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -941,114 +1082,15 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1069,15 +1111,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1099,39 +1132,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1259,6 +1259,67 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>53076</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>121228</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>34634</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74213A29-7CBB-1AC2-F380-9C2698F6EEA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="14721576" y="1939637"/>
+          <a:ext cx="864788" cy="623452"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1585,76 +1646,76 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
     </row>
     <row r="4" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
     </row>
     <row r="5" spans="1:23" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1665,223 +1726,223 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="53"/>
-      <c r="U5" s="53"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
     </row>
     <row r="6" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="48" t="s">
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="74" t="s">
+      <c r="I6" s="53"/>
+      <c r="J6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75"/>
-      <c r="T6" s="75"/>
-      <c r="U6" s="76"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="14"/>
     </row>
     <row r="7" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="70"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="78"/>
-      <c r="T7" s="78"/>
-      <c r="U7" s="79"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="17"/>
     </row>
     <row r="8" spans="1:23" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="63"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="52" t="s">
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="52"/>
-      <c r="J8" s="80" t="s">
+      <c r="I8" s="22"/>
+      <c r="J8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="80"/>
-      <c r="L8" s="52" t="s">
+      <c r="K8" s="18"/>
+      <c r="L8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="52"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="57" t="s">
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="59"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="73"/>
     </row>
     <row r="9" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="52" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="52"/>
-      <c r="J9" s="77" t="s">
+      <c r="I9" s="22"/>
+      <c r="J9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="77"/>
-      <c r="O9" s="77"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="78"/>
-      <c r="R9" s="78"/>
-      <c r="S9" s="78"/>
-      <c r="T9" s="78"/>
-      <c r="U9" s="79"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="17"/>
     </row>
     <row r="10" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="77"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="77"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="78"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="79"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="17"/>
     </row>
     <row r="11" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="52" t="s">
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="52"/>
-      <c r="J11" s="80" t="s">
+      <c r="I11" s="22"/>
+      <c r="J11" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="80"/>
-      <c r="L11" s="52" t="s">
+      <c r="K11" s="18"/>
+      <c r="L11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="57" t="s">
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="59"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
+      <c r="U11" s="73"/>
     </row>
     <row r="12" spans="1:23" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="31" t="s">
+      <c r="C12" s="45"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="31"/>
-      <c r="J12" s="30" t="s">
+      <c r="I12" s="23"/>
+      <c r="J12" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="31" t="s">
+      <c r="K12" s="67"/>
+      <c r="L12" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="60" t="s">
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="Q12" s="61"/>
-      <c r="R12" s="61"/>
-      <c r="S12" s="61"/>
-      <c r="T12" s="61"/>
-      <c r="U12" s="62"/>
+      <c r="Q12" s="75"/>
+      <c r="R12" s="75"/>
+      <c r="S12" s="75"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="76"/>
     </row>
     <row r="13" spans="1:23" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="81" t="str">
+      <c r="C13" s="19" t="str">
         <f>" 합계금액 : 일금 "      &amp; NUMBERSTRING(K20,1) &amp;"원정      (" &amp; DOLLAR(K20) &amp; ")"   &amp;"  (부가세 포함)"</f>
         <v xml:space="preserve"> 합계금액 : 일금 영원정      (₩0)  (부가세 포함)</v>
       </c>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82"/>
-      <c r="O13" s="82"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82"/>
-      <c r="R13" s="82"/>
-      <c r="S13" s="82"/>
-      <c r="T13" s="82"/>
-      <c r="U13" s="83"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="21"/>
       <c r="V13" s="5"/>
     </row>
     <row r="14" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1898,51 +1959,51 @@
       <c r="G14" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="26"/>
-      <c r="J14" s="25" t="s">
+      <c r="I14" s="44"/>
+      <c r="J14" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="73"/>
-      <c r="L14" s="17" t="s">
+      <c r="K14" s="25"/>
+      <c r="L14" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="56"/>
-      <c r="P14" s="17" t="s">
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="19"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="66"/>
     </row>
     <row r="15" spans="1:23" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="15"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="63"/>
+      <c r="P15" s="60"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="61"/>
+      <c r="U15" s="62"/>
       <c r="V15" s="1"/>
     </row>
     <row r="16" spans="1:23" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1971,89 +2032,60 @@
       <c r="W16" s="9"/>
     </row>
     <row r="17" spans="3:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="21" t="s">
+      <c r="D17" s="28"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="34"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
-      <c r="T17" s="37"/>
-      <c r="U17" s="38"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="33"/>
     </row>
     <row r="18" spans="3:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="33" t="s">
+      <c r="D18" s="27"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="35"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="38"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="33"/>
     </row>
     <row r="20" spans="3:21" x14ac:dyDescent="0.3">
       <c r="K20" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J6:U7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:U10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C13:U13"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="L11:O11"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J17:U17"/>
-    <mergeCell ref="J18:U18"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C9:F10"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G6:G12"/>
-    <mergeCell ref="H6:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C8:F8"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C2:U4"/>
     <mergeCell ref="P15:U15"/>
@@ -2069,6 +2101,35 @@
     <mergeCell ref="P12:U12"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C6:F7"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J17:U17"/>
+    <mergeCell ref="J18:U18"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="J6:U7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:U10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C13:U13"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="C9:F10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G6:G12"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="C8:F8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/app_hyup/excel/G_estimate_excel.xlsx
+++ b/assets/app_hyup/excel/G_estimate_excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\jmtech\assets\app_hyup\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76EF8686D38FDC89/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320C8F83-D68A-4366-B2B8-1FAB10F0CA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{E4E2F249-92E9-4F78-8207-91219541296E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D564B44A-6656-496D-9750-194E5521D505}"/>
   <bookViews>
-    <workbookView xWindow="7605" yWindow="930" windowWidth="21600" windowHeight="11295" xr2:uid="{A8E3B584-EFA5-47FD-B92C-1698FC3C9E4C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A8E3B584-EFA5-47FD-B92C-1698FC3C9E4C}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -30,29 +39,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
-    <t>규 격</t>
-  </si>
-  <si>
-    <t>수량</t>
-  </si>
-  <si>
-    <t>세 액</t>
-  </si>
-  <si>
-    <t>공급가액</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">공 
 급
 자 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>단   가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>업    태</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -73,10 +65,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>품목명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>등록번호</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -166,6 +154,30 @@
   </si>
   <si>
     <t xml:space="preserve"> 312-86-30100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도면번호/품명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소재</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수량</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>단위</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>단가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>금액</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -917,6 +929,45 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -947,61 +998,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1013,9 +1010,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1025,12 +1019,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1043,20 +1031,41 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1131,6 +1140,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1179,7 +1191,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1330,9 +1342,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1370,7 +1382,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1476,7 +1488,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1618,7 +1630,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1630,92 +1642,92 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:W20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="4" width="11.625" customWidth="1"/>
+    <col min="3" max="4" width="11.59765625" customWidth="1"/>
     <col min="5" max="5" width="42" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
+    <col min="6" max="6" width="11.59765625" customWidth="1"/>
     <col min="7" max="7" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="11.625" customWidth="1"/>
+    <col min="8" max="11" width="11.59765625" customWidth="1"/>
     <col min="12" max="12" width="8.5" customWidth="1"/>
-    <col min="13" max="13" width="3.875" customWidth="1"/>
-    <col min="14" max="14" width="6.375" customWidth="1"/>
-    <col min="15" max="15" width="4.875" customWidth="1"/>
-    <col min="16" max="20" width="3.875" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+    <col min="14" max="14" width="6.3984375" customWidth="1"/>
+    <col min="15" max="15" width="4.8984375" customWidth="1"/>
+    <col min="16" max="20" width="3.8984375" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="C2" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="C2" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58"/>
+      <c r="U3" s="58"/>
     </row>
-    <row r="4" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="59"/>
+    <row r="4" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:23" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="77" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
+    <row r="5" spans="1:23" ht="21" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C5" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1726,287 +1738,287 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
     </row>
-    <row r="6" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="78" t="s">
+    <row r="6" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="45"/>
+      <c r="J6" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="27"/>
+    </row>
+    <row r="7" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="80"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="30"/>
+    </row>
+    <row r="8" spans="1:23" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="31"/>
+      <c r="L8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="53" t="s">
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="72"/>
+    </row>
+    <row r="9" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C9" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="30"/>
+    </row>
+    <row r="10" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="36"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="30"/>
+    </row>
+    <row r="11" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="31"/>
+      <c r="L11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="53"/>
-      <c r="J6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="14"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="72"/>
     </row>
-    <row r="7" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="81"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="17"/>
+    <row r="12" spans="1:23" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C12" s="39"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="35"/>
+      <c r="J12" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="66"/>
+      <c r="L12" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="74"/>
+      <c r="T12" s="74"/>
+      <c r="U12" s="75"/>
     </row>
-    <row r="8" spans="1:23" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="56"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="18"/>
-      <c r="L8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="71" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="73"/>
-    </row>
-    <row r="9" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="22"/>
-      <c r="J9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="17"/>
-    </row>
-    <row r="10" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="41"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="17"/>
-    </row>
-    <row r="11" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="73"/>
-    </row>
-    <row r="12" spans="1:23" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="45"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="23"/>
-      <c r="J12" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="67"/>
-      <c r="L12" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="76"/>
-    </row>
-    <row r="13" spans="1:23" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="19" t="str">
+    <row r="13" spans="1:23" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C13" s="32" t="str">
         <f>" 합계금액 : 일금 "      &amp; NUMBERSTRING(K20,1) &amp;"원정      (" &amp; DOLLAR(K20) &amp; ")"   &amp;"  (부가세 포함)"</f>
         <v xml:space="preserve"> 합계금액 : 일금 영원정      (₩0)  (부가세 포함)</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="21"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="34"/>
       <c r="V13" s="5"/>
     </row>
-    <row r="14" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="55"/>
+    <row r="14" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="24"/>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="44"/>
-      <c r="J14" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="25"/>
-      <c r="L14" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="66"/>
+      <c r="H14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="83"/>
+      <c r="L14" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="64"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="65"/>
     </row>
-    <row r="15" spans="1:23" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="63"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="61"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="62"/>
+    <row r="15" spans="1:23" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C15" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="60"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="60"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="61"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:23" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
@@ -2031,62 +2043,61 @@
       <c r="V16" s="11"/>
       <c r="W16" s="9"/>
     </row>
-    <row r="17" spans="3:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="29"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="33"/>
+    <row r="17" spans="3:21" ht="31.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C17" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="48"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="49"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="52"/>
+      <c r="T17" s="52"/>
+      <c r="U17" s="53"/>
     </row>
-    <row r="18" spans="3:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="33"/>
+    <row r="18" spans="3:21" ht="31.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C18" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="47"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="50"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="52"/>
+      <c r="Q18" s="52"/>
+      <c r="R18" s="52"/>
+      <c r="S18" s="52"/>
+      <c r="T18" s="52"/>
+      <c r="U18" s="53"/>
     </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:21" x14ac:dyDescent="0.4">
       <c r="K20" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="C11:F11"/>
     <mergeCell ref="C2:U4"/>
     <mergeCell ref="P15:U15"/>
     <mergeCell ref="L15:O15"/>
@@ -2110,7 +2121,6 @@
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="H14:I14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="C14:D14"/>
@@ -2126,10 +2136,12 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="G6:G12"/>
     <mergeCell ref="H6:I7"/>
+    <mergeCell ref="C11:F11"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="H9:I10"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="C8:F8"/>
+    <mergeCell ref="H14:I14"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
